--- a/GourmetProject/GameConfig/Datas/score_profile.xlsx
+++ b/GourmetProject/GameConfig/Datas/score_profile.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,72 +456,86 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>分数曲线ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>基础目标分</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>普通难度倍率</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Boss倍率</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>无尽增长倍率</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>目标分取整粒度</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>score_w1</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>80</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>score_w2</t>
+          <t>score_w1</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -540,11 +554,11 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>score_w3</t>
+          <t>score_w2</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -563,11 +577,11 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>score_w4</t>
+          <t>score_w3</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -586,11 +600,11 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>score_w5</t>
+          <t>score_w4</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>480</v>
+        <v>320</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -609,11 +623,11 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>score_w6</t>
+          <t>score_w5</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>700</v>
+        <v>480</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -632,11 +646,11 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>score_w7</t>
+          <t>score_w6</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -655,11 +669,11 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>score_w8</t>
+          <t>score_w7</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -671,6 +685,29 @@
         <v>1.5</v>
       </c>
       <c r="G10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>score_w8</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G11" t="n">
         <v>10</v>
       </c>
     </row>
